--- a/node-fleet-shopping-list.xlsx
+++ b/node-fleet-shopping-list.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>One pair per room, mounted off-box. Must be the analog-input model (original; V2 currently unavailable, V3/Pro are USB-audio — wrong).</t>
+          <t>One pair per room, mounted off-box. Must be the analog-input model (original; V2 currently unavailable, V3/Pro are USB-audio — wrong). Dell AC511 soundbar considered/rejected 2026-07-19 (analog aux-in confirmed in Dell manual so it would work, but 2.5W vs Pebble 4.4W and no real price win — sticking with Pebbles).</t>
         </is>
       </c>
     </row>
@@ -967,19 +967,27 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Miady 2-Pack 20000mAh PD 22.5W power bank (74Wh; 2x USB-A + 1x USB-C out per bank)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>2</v>
+          <t>USB battery banks — EXISTING on-hand fleet (Miady 2-pack = top-up/replacement reference)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>16 + spares</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>YES — existing banks (Tim 2026-07-19)</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0GQM3SB65</t>
@@ -987,7 +995,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>$28.99/pair White+Black ($14.50/bank; Black+Black $32.99) @2026-07-19. 15 rooms + mast router + 2 rotation spares. Room plug set per bank: Pebble captive A-male -&gt; USB-A, node &lt;- 1ft A-to-C. ~50Wh usable = 2 nights/room with margin. Box draws ~0.2A continuous = 3-4x above cheap-bank auto-off thresholds. Velcro bank OUTSIDE the box (swap without opening; shade it). BENCH GATE before fleet buy: one bank + node + Pebble overnight, audio duty-cycling, ESPHome uptime = witness. Fallback if Miady QC disappoints: INIU 20000mAh 22.5W single $29.99 (dp/B0DFLSQBHT).</t>
+          <t>BUY NONE — on-hand banks, DAY SHIFT ONLY (generator runs all evening/night and covers the boxes via wall cubes on the fixture AC runs; banks recharge overnight at their own boxes). Day = ~15-25Wh -&gt; any bank &gt;=10000mAh covers it; big banks to loud rooms + the server Pi (biggest day load, 50-70Wh). Per-bank requirement: &gt;=2 outputs incl. one USB-A (Pebble captive plug is A-male) + holds ~0.2A without auto-off (10-min node test, cull flunkers). Pass-through check sorts the fleet: output stays live while charging = bank stays inline 24/7 (no daily flips); else flip plugs cube&lt;-&gt;bank at dusk/dawn. Top-up ref if short: Miady 2-pk 20000mAh $28.99 (this URL) or INIU single $29.99 (dp/B0DFLSQBHT).</t>
         </is>
       </c>
     </row>
@@ -999,17 +1007,23 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Anker PowerPort 6 desktop charger, 60W, 6x USB-A 2.4A</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>1</v>
+          <t>Night AC-&gt;USB wall cubes (PowerPort-6-class 6-port, 1 per 2 adjacent rooms) — AUDIT DRAWER FIRST</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>~3 A-ports per room at night</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0-8 after drawer audit</t>
+        </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr">
@@ -1019,7 +1033,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>REPURPOSED in v4: the day-charge rack, not a UPS part. 6x 2.4A ports on generator/camp power; each bank needs a slot every other day = ~9 banks/day in two ~2h waves; the 2 spare banks float the rotation.</t>
+          <t>Night feed: node + Pebble + bank-charge (~15W/room) off the same backstage AC runs the DMX fixtures use. Any 2-3 port cubes from the drawer work (per room); a 6-port PowerPort-6-class shared between two adjacent rooms (7ft apart, 10ft leads) fills gaps if buying. Banks that pass through only need ONE port (bank input).</t>
         </is>
       </c>
     </row>
@@ -1288,24 +1302,24 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Power topology (v4 — one cheap 20000mAh bank velcro-d at every box; stations dead)</t>
+          <t>Power topology (v5 — generator = night power; existing banks = day shift only)</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Per room: Miady 20000mAh bank at the box -&gt; node USB-C (1ft A-to-C) + Pebble captive A-male direct. No stations, no long 5V runs (the 30-50ft droop rule is WHY banks sit at the boxes). ~18-24Wh per 12h room-night vs ~50Wh usable = 2 nights/charge; day-charge rotation on one PowerPort 6 (~9 banks/day, two waves). Router on the mast gets bank #16; swap daily if WiFi runs 24/7. v3 (3x SOLIX C300 cluster stations, ~$840) superseded 2026-07-19: ~$260 of banks does the same 5V job and a bank failure is a one-room 60-second swap, not a 5-room event.</t>
+          <t>Tim 2026-07-19: generator runs ALL evening/night (same AC as the DMX fixtures backstage); banks only bridge the ~12h day. NIGHT: box gear on a wall cube off the fixture runs, room bank recharging on the same cube (~3 A-ports/room). DAY: bank carries the box (~15-25Wh; &gt;=10000mAh = covered). Daily flip = 2x 10-second plug moves (dawn gear-&gt;bank, dusk gear-&gt;cube + bank-&gt;charge port); pass-through banks skip flips (inline 24/7, cube feeds input at night; dusk plug-in blip = one harmless node reboot). Router bank charges in place overnight via 10ft A-extension (droop just slows charging) or daily swap. Server Pi = biggest day load (50-70Wh): earmark the largest bank(s). No charge rack, no rotation. Supersede chain: v3 3x SOLIX stations ($840) -&gt; v4 per-box banks 24/7 -&gt; v5 banks day-only (generator owns night).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>The one test that gates the big buy</t>
+          <t>The test that gates install week</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Bench ONE Miady bank + node + Pebble overnight with audio duty-cycling BEFORE buying 9 packs: morning check = still powered, no port flap (ESPHome uptime sensor is the witness). The ~0.2A continuous box draw sits 3-4x above cheap-bank auto-off thresholds, but the timer lesson from v3 research says verify on the real unit anyway.</t>
+          <t>Per-bank, before install week: (1) 10 min under a node (~0.2A) — cull auto-off flunkers to phone duty; (2) pass-through check — plug charge input while loaded: output stays live = "inline 24/7" pile, output dies while charging = "flip" pile (a brief blip on plug-in is fine = one node reboot at dusk). Then one representative bank + node + Pebble through a full day-shift discharge with audio duty-cycling (ESPHome uptime sensor = witness).</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1331,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>PAM8403 amp, CQRobot speaker, 470-1000uF cap, USB breakout, 1N5817, per-room wall cubes, per-box V50 banks: all deleted by the DAC-line-out-into-Pebble design and the per-box bank topology (v4: cheap Miady banks; V50s were the gold-plated version of the same idea; SOLIX C300 stations lived one day as v3 before Tim called cheapo banks). CQRobot specifically rejected: verified ~76-77dB/W sensitivity (too quiet). Pebble V3/Pro are USB-audio devices - do not substitute for the analog Pebble/Pebble V2.</t>
+          <t>PAM8403 amp, CQRobot speaker, 470-1000uF cap, USB breakout, 1N5817, per-box V50 banks: deleted by the DAC-line-out-into-Pebble design and the v5 power split (V50s were the gold-plated per-box idea; SOLIX C300 stations lived one day as v3; wall cubes are BACK in v5 as the night AC feed — see the cube row). CQRobot specifically rejected: verified ~76-77dB/W sensitivity (too quiet). Pebble V3/Pro are USB-audio devices - do not substitute for the analog Pebble/Pebble V2.</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1343,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>15 rooms. Ordered 7/18: 1x S3 3-pack, 1x DAC 2-pack (= the bench kit), microswitch 10-pack, piezo 20-pack, arcade 5-pack — those rows are DONE. On hand: 3x LD2410C, 2x VL53L1X (both the right modules). Remaining to buy: 5x S3 3-packs, 7x DAC 2-packs, 5x LD2410C 2-packs, 4 more VL53L1X, Pebbles (15 minus owned), 9x Miady bank 2-packs, 1x PowerPort 6 (charge rack), short A-to-C cables, clamps, router.</t>
+          <t>15 rooms. Ordered 7/18: 1x S3 3-pack, 1x DAC 2-pack (= the bench kit), microswitch 10-pack, piezo 20-pack, arcade 5-pack — those rows are DONE. On hand: 3x LD2410C, 2x VL53L1X (both the right modules). Remaining to buy: 5x S3 3-packs, 7x DAC 2-packs, 5x LD2410C 2-packs, 4 more VL53L1X, Pebbles (15 minus owned), wall cubes only if the drawer audit comes up short, short A-to-C cables, clamps, router.</t>
         </is>
       </c>
     </row>
